--- a/Fullmer_etal_2025/Figures_Tables/Figure2/OldNodesBS_Plotting.xlsx
+++ b/Fullmer_etal_2025/Figures_Tables/Figure2/OldNodesBS_Plotting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nickm/GitHub/FullmerMatzke25/Fullmer_etal_2025/Figures_Tables/Figure2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6096D-C66A-E142-A951-698D1B0B0C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555DE142-13CB-0E44-A36F-6E28EE4EF19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16380" yWindow="500" windowWidth="21020" windowHeight="22400" xr2:uid="{BEDB55F5-3D0D-5E41-95A2-DA312CACB3A7}"/>
   </bookViews>
